--- a/Statistics/Section 3 - Inferential Statistics Fundamentals/4_The Standard Normal Distribution/3.4.Standard-normal-distribution-exercise - completed.xlsx
+++ b/Statistics/Section 3 - Inferential Statistics Fundamentals/4_The Standard Normal Distribution/3.4.Standard-normal-distribution-exercise - completed.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics\Section 3 - Inferential Statistics Fundamentals\4_The Standard Normal Distribution\Exercises\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\slong\365 Data Science\Statistics_\Section 3 - Inferential Statistics Fundamentals_\4_The Standard Normal Distribution\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E8D871-930F-47D8-B9B3-4BB3CE405C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD86F32D-8809-4926-9876-82B84D15EAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="Standard normal" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Standard normal'!$B$15</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Standard normal'!$B$16:$B$95</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Standard normal'!$F$15</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Standard normal'!$F$16:$F$95</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Standard normal'!$D$15</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">'Standard normal'!$D$16:$D$95</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Standard normal'!$F$15</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Standard normal'!$F$16:$F$95</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Standard normal'!$D$15</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Standard normal'!$D$16:$D$95</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Standard normal'!$B$15</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'Standard normal'!$B$16:$B$95</definedName>
     <definedName name="_xlchart.v1.6" hidden="1">'Standard normal'!$F$15</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">'Standard normal'!$F$16:$F$95</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Standard normal'!$A$1:$V$53</definedName>
@@ -219,7 +219,7 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.5</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -257,7 +257,7 @@
         <cx:series layoutId="clusteredColumn" uniqueId="{744BAFFE-3839-4C0B-86D7-294CA4E39DC8}" formatIdx="0">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:f>_xlchart.v1.4</cx:f>
               <cx:v>Original dataset</cx:v>
             </cx:txData>
           </cx:tx>
@@ -286,45 +286,54 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.5</cx:f>
+        <cx:f>_xlchart.v1.3</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:txData>
-          <cx:v>Substraction of the Mean i.e. variance (from each orginal dataset)</cx:v>
-        </cx:txData>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              </a:rPr>
+              <a:t>Substraction of the Mean from each orginal dataset - </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              </a:rPr>
+              <a:t>Mean is now 0</a:t>
+            </a:r>
+          </a:p>
+        </cx:rich>
       </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Substraction of the Mean i.e. variance (from each orginal dataset)</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{5D277D8D-C202-485C-B04E-5C5C53AC721A}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:f>_xlchart.v1.2</cx:f>
               <cx:v>Subtract Mean</cx:v>
             </cx:txData>
           </cx:tx>
@@ -353,45 +362,54 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.3</cx:f>
+        <cx:f>_xlchart.v1.1</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
     <cx:title pos="t" align="ctr" overlay="0">
       <cx:tx>
-        <cx:txData>
-          <cx:v>Variance divided by Standard Deviation (Standardise original graph)</cx:v>
-        </cx:txData>
+        <cx:rich>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              </a:rPr>
+              <a:t>(Mean - Variance)/Standard Deviation - </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1400" b="0" i="1" u="none" strike="noStrike" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              </a:rPr>
+              <a:t>Standard Deviation is now 1</a:t>
+            </a:r>
+          </a:p>
+        </cx:rich>
       </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Variance divided by Standard Deviation (Standardise original graph)</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
         <cx:series layoutId="clusteredColumn" uniqueId="{2E842438-E3CC-4408-8093-E7ED0CB522DB}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:f>_xlchart.v1.0</cx:f>
               <cx:v>Divide by std</cx:v>
             </cx:txData>
           </cx:tx>
@@ -2998,7 +3016,7 @@
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="7">
-        <f t="shared" ref="F17:F80" si="1">D18/$F$12</f>
+        <f t="shared" ref="F18:F80" si="1">D18/$F$12</f>
         <v>-2.3211113758835213</v>
       </c>
       <c r="G18" s="9"/>
